--- a/Data/MediStation - 3791910009/MediStation - 3791910009.xlsx
+++ b/Data/MediStation - 3791910009/MediStation - 3791910009.xlsx
@@ -66,7 +66,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <charset val="129"/>
       </rPr>
@@ -108,7 +108,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <charset val="129"/>
       </rPr>
@@ -128,7 +128,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <charset val="129"/>
       </rPr>
@@ -142,7 +142,7 @@
         <family val="1"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">.</t>
     </r>
   </si>
   <si>
@@ -201,7 +201,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <charset val="129"/>
       </rPr>
@@ -221,7 +221,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <charset val="129"/>
       </rPr>
@@ -241,7 +241,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <charset val="129"/>
       </rPr>
@@ -255,73 +255,253 @@
         <family val="1"/>
         <charset val="129"/>
       </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ThingDef+MS_GojuiceStation.comps.4.fuelLabel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_GojuiceStation.comps.4.fuelLabel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Go-juice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고주스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ThingDef+MS_GojuiceStation.comps.4.fuelGizmoLabel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_GojuiceStation.comps.4.fuelGizmoLabel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ThingDef+MS_GojuiceStation.comps.4.outOfFuelMessage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_GojuiceStation.comps.4.outOfFuelMessage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Out of go-juice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고주스 없음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+MS_MediStation_SetRefuelThreshold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_MediStation_SetRefuelThreshold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set refuel threshold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">자동 보충 기준 설정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+MS_MediStation_SetRefuelThresholdDesc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_MediStation_SetRefuelThresholdDesc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set the medicine level below which colonists will automatically restock this MediStation to full capacity.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">의료 스테이션의 약품이 이 수치 미만으로 떨어지면 정착민들이 최대 용량까지 자동으로 보충합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+MS_MediStation_RefuelThresholdInspect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_MediStation_RefuelThresholdInspect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto-refuel threshold: {0}</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">자동 보충 기준</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: {0}</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+MS_MediStation_ToggleAutoRefuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_MediStation_ToggleAutoRefuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto-refuel medicine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">약품 자동 보충</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+MS_MediStation_ToggleAutoRefuelDesc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_MediStation_ToggleAutoRefuelDesc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whether colonists will automatically keep this MediStation stocked with medicine: {ONOFF}.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">정착민들이 의료 스테이션의 약품을 자동으로 보충할지 설정합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: {ONOFF}.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+MS_MediStation_EjectMedicine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_MediStation_EjectMedicine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eject medicine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">약품 꺼내기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+MS_MediStation_EjectMedicineDesc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_MediStation_EjectMedicineDesc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eject all stored medicine back onto the ground.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">보관된 약품을 모두 꺼냅니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+MS_MediStation_AllowGuests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_MediStation_AllowGuests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allow guests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">방문객 사용 허용</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+MS_MediStation_AllowGuestsDesc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_MediStation_AllowGuestsDesc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allow non-colonist humanlike pawns to use this MediStation. Non-hostile faction members who receive treatment here are considered rescued upon leaving the map.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">정착민이 아닌 사람도 이 의료 스테이션을 사용할 수 있도록 허용합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">. </t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">ThingDef+MS_GojuiceStation.comps.4.fuelLabel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_GojuiceStation.comps.4.fuelLabel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Go-juice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고주스</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ThingDef+MS_GojuiceStation.comps.4.fuelGizmoLabel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_GojuiceStation.comps.4.fuelGizmoLabel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ThingDef+MS_GojuiceStation.comps.4.outOfFuelMessage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_GojuiceStation.comps.4.outOfFuelMessage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Out of go-juice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고주스 없음</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+MS_MediStation_SetRefuelThreshold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_MediStation_SetRefuelThreshold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set refuel threshold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">자동 보충 기준 설정</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+MS_MediStation_SetRefuelThresholdDesc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_MediStation_SetRefuelThresholdDesc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set the medicine level below which colonists will automatically restock this MediStation to full capacity.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">의료 스테이션의 약품이 이 수치 미만으로 떨어지면 정착민들이 최대 용량까지 자동으로 보충합니다</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">이곳에서 치료받은 비적대 세력 구성원은 지도를 떠날 때 구조된 것으로 간주됩니다</t>
     </r>
     <r>
       <rPr>
@@ -335,25 +515,96 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+MS_MediStation_RefuelThresholdInspect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_MediStation_RefuelThresholdInspect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto-refuel threshold: {0}</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">자동 보충 기준</t>
-    </r>
+    <t xml:space="preserve">Keyed+MS_MediStation_UseMediStation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_MediStation_UseMediStation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use MediStation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">의료 스테이션 사용</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+MS_MediStation_NoWoundsToTend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_MediStation_NoWoundsToTend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no wounds to tend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">치료할 상처 없음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+MS_MediStation_NotAvailable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_MediStation_NotAvailable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not available</t>
+  </si>
+  <si>
+    <t xml:space="preserve">사용 불가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+MS_MediStation_SwitchedOff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_MediStation_SwitchedOff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">switched off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전원 꺼짐</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+MS_MediStation_NoMedicine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_MediStation_NoMedicine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no medicine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+MS_MediStation_ReservedForPrisoners</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_MediStation_ReservedForPrisoners</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reserved for prisoners</t>
+  </si>
+  <si>
+    <t xml:space="preserve">수감자 전용</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+MS_MediStation_ColonistsOnly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_MediStation_ColonistsOnly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">colonists only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">정착민 전용</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+MS_MediStation_TreatingReport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_MediStation_TreatingReport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{0} treating at {1}</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -362,40 +613,44 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: {0}</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+MS_MediStation_ToggleAutoRefuel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_MediStation_ToggleAutoRefuel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto-refuel medicine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">약품 자동 보충</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+MS_MediStation_ToggleAutoRefuelDesc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_MediStation_ToggleAutoRefuelDesc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whether colonists will automatically keep this MediStation stocked with medicine: {ONOFF}.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">정착민들이 의료 스테이션의 약품을 자동으로 보충할지 설정합니다</t>
+      <t xml:space="preserve">{0}: {1}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">에서 치료받는 중</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+MS_GojuiceStation_SetRefuelThreshold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_GojuiceStation_SetRefuelThreshold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+MS_GojuiceStation_SetRefuelThresholdDesc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_GojuiceStation_SetRefuelThresholdDesc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set the go-juice level below which colonists will automatically restock this GojuiceStation to full capacity.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">고주스 분무기의 고주스가 이 수치 미만으로 떨어지면 정착민들이 최대 용량까지 자동으로 보충합니다</t>
     </r>
     <r>
       <rPr>
@@ -405,40 +660,89 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+MS_GojuiceStation_RefuelThresholdInspect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_GojuiceStation_RefuelThresholdInspect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+MS_GojuiceStation_ToggleAutoRefuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_GojuiceStation_ToggleAutoRefuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto-refuel go-juice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고주스 자동 보충</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+MS_GojuiceStation_ToggleAutoRefuelDesc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_GojuiceStation_ToggleAutoRefuelDesc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whether colonists will automatically keep this GojuiceStation stocked with go-juice: {ONOFF}.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">정착민들이 고주스 분무기의 고주스를 자동으로 보충할지 설정합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">: {ONOFF}.</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+MS_MediStation_EjectMedicine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_MediStation_EjectMedicine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eject medicine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">약품 꺼내기</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+MS_MediStation_EjectMedicineDesc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_MediStation_EjectMedicineDesc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eject all stored medicine back onto the ground.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">보관된 약품을 모두 꺼냅니다</t>
+    <t xml:space="preserve">Keyed+MS_GojuiceStation_EjectMedicine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_GojuiceStation_EjectMedicine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eject go-juice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고주스 꺼내기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+MS_GojuiceStation_EjectMedicineDesc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_GojuiceStation_EjectMedicineDesc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eject all stored go-juice back onto the ground.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">보관된 고주스를 모두 꺼냅니다</t>
     </r>
     <r>
       <rPr>
@@ -452,36 +756,30 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+MS_MediStation_AllowGuests</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_MediStation_AllowGuests</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allow guests</t>
-  </si>
-  <si>
-    <t xml:space="preserve">방문객 사용 허용</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+MS_MediStation_AllowGuestsDesc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_MediStation_AllowGuestsDesc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allow non-colonist humanlike pawns to use this MediStation. Non-hostile faction members who receive treatment here are considered rescued upon leaving the map.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">정착민이 아닌 사람도 이 의료 스테이션을 사용할 수 있도록 허용합니다</t>
+    <t xml:space="preserve">Keyed+MS_GojuiceStation_AllowGuests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_GojuiceStation_AllowGuests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+MS_GojuiceStation_AllowGuestsDesc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_GojuiceStation_AllowGuestsDesc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allow non-colonist humanlike pawns to use this Go-juice Nebulizer. Non-hostile faction members who receive a dose here are considered rescued upon leaving the map.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">정착민이 아닌 사람도 이 고주스 분무기를 사용할 수 있도록 허용합니다</t>
     </r>
     <r>
       <rPr>
@@ -497,11 +795,11 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">이곳에서 치료받은 비적대 세력 구성원은 지도를 떠날 때 구조된 것으로 간주됩니다</t>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">이곳에서 고주스를 투여받은 비적대 세력 구성원은 지도를 떠날 때 구조된 것으로 간주됩니다</t>
     </r>
     <r>
       <rPr>
@@ -515,94 +813,58 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+MS_MediStation_UseMediStation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_MediStation_UseMediStation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use MediStation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">의료 스테이션 사용</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+MS_MediStation_NoWoundsToTend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_MediStation_NoWoundsToTend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no wounds to tend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">치료할 상처 없음</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+MS_MediStation_NotAvailable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_MediStation_NotAvailable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not available</t>
-  </si>
-  <si>
-    <t xml:space="preserve">사용 불가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+MS_MediStation_SwitchedOff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_MediStation_SwitchedOff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">switched off</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전원 꺼짐</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+MS_MediStation_NoMedicine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_MediStation_NoMedicine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no medicine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+MS_MediStation_ReservedForPrisoners</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_MediStation_ReservedForPrisoners</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reserved for prisoners</t>
-  </si>
-  <si>
-    <t xml:space="preserve">수감자 전용</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+MS_MediStation_ColonistsOnly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_MediStation_ColonistsOnly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">colonists only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">정착민 전용</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+MS_MediStation_TreatingReport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_MediStation_TreatingReport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{0} treating at {1}</t>
+    <t xml:space="preserve">Keyed+MS_GojuiceStation_UseStation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_GojuiceStation_UseStation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use Go-juice Nebulizer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고주스 분무기 사용</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+MS_GojuiceStation_NotAvailable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_GojuiceStation_NotAvailable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+MS_GojuiceStation_SwitchedOff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_GojuiceStation_SwitchedOff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+MS_GojuiceStation_NoGoJuice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_GojuiceStation_NoGoJuice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no go-juice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+MS_GojuiceStation_ReservedForPrisoners</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_GojuiceStation_ReservedForPrisoners</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+MS_GojuiceStation_ColonistsOnly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_GojuiceStation_ColonistsOnly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+MS_GojuiceStation_AdministeringReport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_GojuiceStation_AdministeringReport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{0} inhaling at {1}</t>
   </si>
   <si>
     <r>
@@ -619,269 +881,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">에서 치료받는 중</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+MS_GojuiceStation_SetRefuelThreshold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_GojuiceStation_SetRefuelThreshold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+MS_GojuiceStation_SetRefuelThresholdDesc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_GojuiceStation_SetRefuelThresholdDesc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set the go-juice level below which colonists will automatically restock this GojuiceStation to full capacity.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">고주스 분무기의 고주스가 이 수치 미만으로 떨어지면 정착민들이 최대 용량까지 자동으로 보충합니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+MS_GojuiceStation_RefuelThresholdInspect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_GojuiceStation_RefuelThresholdInspect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+MS_GojuiceStation_ToggleAutoRefuel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_GojuiceStation_ToggleAutoRefuel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto-refuel go-juice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고주스 자동 보충</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+MS_GojuiceStation_ToggleAutoRefuelDesc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_GojuiceStation_ToggleAutoRefuelDesc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whether colonists will automatically keep this GojuiceStation stocked with go-juice: {ONOFF}.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">정착민들이 고주스 분무기의 고주스를 자동으로 보충할지 설정합니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: {ONOFF}.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+MS_GojuiceStation_EjectMedicine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_GojuiceStation_EjectMedicine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eject go-juice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고주스 꺼내기</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+MS_GojuiceStation_EjectMedicineDesc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_GojuiceStation_EjectMedicineDesc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eject all stored go-juice back onto the ground.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">보관된 고주스를 모두 꺼냅니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+MS_GojuiceStation_AllowGuests</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_GojuiceStation_AllowGuests</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+MS_GojuiceStation_AllowGuestsDesc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_GojuiceStation_AllowGuestsDesc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allow non-colonist humanlike pawns to use this Go-juice Nebulizer. Non-hostile faction members who receive a dose here are considered rescued upon leaving the map.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">정착민이 아닌 사람도 이 고주스 분무기를 사용할 수 있도록 허용합니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">이곳에서 고주스를 투여받은 비적대 세력 구성원은 지도를 떠날 때 구조된 것으로 간주됩니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+MS_GojuiceStation_UseStation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_GojuiceStation_UseStation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use Go-juice Nebulizer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고주스 분무기 사용</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+MS_GojuiceStation_NotAvailable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_GojuiceStation_NotAvailable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+MS_GojuiceStation_SwitchedOff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_GojuiceStation_SwitchedOff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+MS_GojuiceStation_NoGoJuice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_GojuiceStation_NoGoJuice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no go-juice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+MS_GojuiceStation_ReservedForPrisoners</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_GojuiceStation_ReservedForPrisoners</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+MS_GojuiceStation_ColonistsOnly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_GojuiceStation_ColonistsOnly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+MS_GojuiceStation_AdministeringReport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_GojuiceStation_AdministeringReport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{0} inhaling at {1}</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">{0}: {1}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <charset val="129"/>
       </rPr>
@@ -896,7 +896,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -937,16 +937,9 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Segoe UI"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
     </font>
@@ -961,7 +954,7 @@
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Segoe UI"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
     </font>
@@ -1021,19 +1014,19 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1566,7 +1559,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>67</v>
       </c>
@@ -1906,7 +1899,7 @@
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
     </row>
-    <row r="35" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>130</v>
       </c>
